--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487573_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487573_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3514</v>
+        <v>5.212</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5752</v>
+        <v>6.2486</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2238</v>
+        <v>-1.0367</v>
       </c>
       <c r="G2" t="n">
         <v>2.8201</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4099</v>
+        <v>0.4507</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.607</v>
+        <v>0.0665</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1971</v>
+        <v>0.3842</v>
       </c>
       <c r="V2" t="n">
         <v>1.5495</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.0385</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5987</v>
+        <v>0.394</v>
       </c>
       <c r="F3" t="n">
-        <v>1.591</v>
+        <v>1.6445</v>
       </c>
       <c r="G3" t="n">
         <v>3.0563</v>
@@ -688,13 +688,13 @@
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3085</v>
+        <v>0.1573</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3258</v>
+        <v>0.1212</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0173</v>
+        <v>0.0362</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0429</v>
+        <v>1.4344</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3849</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.658</v>
+        <v>1.1844</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7843</v>
+        <v>-2.2462</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8051</v>
+        <v>-3.9484</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0208</v>
+        <v>1.7023</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1521</v>
+        <v>0.5058</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2624</v>
+        <v>-1.9788</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4145</v>
+        <v>2.4846</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9364</v>
+        <v>-2.752</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5427</v>
+        <v>-1.9696</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3938</v>
+        <v>-0.7823</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3709</v>
+        <v>3.3294</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5668</v>
+        <v>3.5253</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0645</v>
+        <v>0.3511</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4286</v>
+        <v>-0.06</v>
       </c>
       <c r="U4" t="n">
-        <v>0.636</v>
+        <v>0.4111</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.736</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1654</v>
+        <v>0.3186</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6639</v>
+        <v>0.4174</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3028</v>
+        <v>-0.7843</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9187</v>
+        <v>-1.8051</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6159</v>
+        <v>1.0208</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1784</v>
+        <v>0.1521</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0323</v>
+        <v>-1.2624</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1461</v>
+        <v>1.4145</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4812</v>
+        <v>-0.9364</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.951</v>
+        <v>-0.5427</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5302</v>
+        <v>-0.3938</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1005</v>
+        <v>0.7577</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0129</v>
+        <v>0.3623</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1134</v>
+        <v>0.3954</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4129</v>
+        <v>0.3517</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1992</v>
+        <v>1.1225</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6121</v>
+        <v>-0.7708</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2462</v>
+        <v>-0.3028</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.9484</v>
+        <v>-0.9187</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7023</v>
+        <v>0.6159</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5058</v>
+        <v>1.1784</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9788</v>
+        <v>0.0323</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4846</v>
+        <v>1.1461</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.752</v>
+        <v>-1.4812</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9696</v>
+        <v>-0.951</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7823</v>
+        <v>-0.5302</v>
       </c>
       <c r="P6" t="n">
-        <v>3.3294</v>
+        <v>0.9792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.5253</v>
+        <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6704</v>
+        <v>-0.0494</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5092</v>
+        <v>-0.0559</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8388</v>
+        <v>0.0065</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0228</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1131</v>
+        <v>-1.3093</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0903</v>
+        <v>1.4024</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7591</v>
+        <v>-3.2782</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5545</v>
+        <v>-1.864</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3137</v>
+        <v>-1.4142</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4445</v>
+        <v>-1.4803</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4357</v>
+        <v>-0.4391</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8802</v>
+        <v>-1.0412</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3146</v>
+        <v>-1.7979</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8812</v>
+        <v>-1.4249</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5666</v>
+        <v>-0.373</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3502</v>
+        <v>3.1336</v>
       </c>
       <c r="S7" t="n">
-        <v>0.931</v>
+        <v>-0.0791</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8763</v>
+        <v>-0.1459</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0547</v>
+        <v>0.0668</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3905</v>
+        <v>1.492</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3905</v>
+        <v>1.492</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.71</v>
+        <v>-0.7821</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3982</v>
+        <v>-2.8723</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1082</v>
+        <v>2.0903</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9369</v>
+        <v>-0.7591</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3154</v>
+        <v>0.5545</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6214</v>
+        <v>-1.3137</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5849</v>
+        <v>-0.4445</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1603</v>
+        <v>1.4357</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5755</v>
+        <v>-1.8802</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.352</v>
+        <v>-0.3146</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1551</v>
+        <v>-0.8812</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1969</v>
+        <v>0.5666</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>2.3502</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3847</v>
+        <v>0.1717</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4911</v>
+        <v>0.117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1064</v>
+        <v>0.0547</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2754</v>
+        <v>-0.3905</v>
       </c>
       <c r="W8" t="n">
-        <v>1.492</v>
+        <v>-0.3905</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3117</v>
+        <v>-0.8134</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5538</v>
+        <v>1.1076</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2421</v>
+        <v>-1.9211</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2782</v>
+        <v>-2.9369</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.864</v>
+        <v>-2.3154</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4142</v>
+        <v>-0.6214</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4803</v>
+        <v>-0.5849</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4391</v>
+        <v>-1.1603</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0412</v>
+        <v>0.5755</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7979</v>
+        <v>-2.352</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4249</v>
+        <v>-1.1551</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.373</v>
+        <v>-1.1969</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1336</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.484</v>
+        <v>0.2813</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3904</v>
+        <v>0.2005</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0936</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>1.492</v>
+        <v>0.2754</v>
       </c>
       <c r="W9" t="n">
         <v>1.492</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8624</v>
+        <v>-2.7822</v>
       </c>
       <c r="E10" t="n">
         <v>-2.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2624</v>
+        <v>-0.1822</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3321</v>
@@ -1234,13 +1234,13 @@
         <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4923</v>
+        <v>-0.4121</v>
       </c>
       <c r="T10" t="n">
         <v>-0.297</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1953</v>
+        <v>-0.1151</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2754</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2016</v>
+        <v>-3.5041</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6076</v>
+        <v>-2.0169</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5941</v>
+        <v>-1.4872</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4029</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9847</v>
+        <v>0.6822</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1269</v>
+        <v>0.7175</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1422</v>
+        <v>-0.0353</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8249</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.389899999999999</v>
+        <v>1.983999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04869999999999952</v>
+        <v>0.6427999999999994</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3411</v>
+        <v>1.341</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.166099999999998</v>
+        <v>-5.166099999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-7.843099999999999</v>
@@ -1366,10 +1366,10 @@
         <v>5.4952</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3853</v>
+        <v>-0.3853000000000003</v>
       </c>
       <c r="L12" t="n">
-        <v>5.8807</v>
+        <v>5.880700000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-10.6612</v>
@@ -1381,7 +1381,7 @@
         <v>-3.2035</v>
       </c>
       <c r="P12" t="n">
-        <v>4.896099999999999</v>
+        <v>4.896100000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.73</v>
@@ -1390,16 +1390,16 @@
         <v>17.6263</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7173</v>
+        <v>2.3114</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4321999999999999</v>
+        <v>1.0262</v>
       </c>
       <c r="U12" t="n">
         <v>1.2852</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.05759999999999987</v>
+        <v>-0.05759999999999943</v>
       </c>
       <c r="W12" t="n">
         <v>6.851599999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. LOPEZ CAMIÑA</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6403</v>
+        <v>4.112</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2826</v>
+        <v>3.7387</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3577</v>
+        <v>0.3733</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.891</v>
+        <v>2.4457</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0119</v>
+        <v>0.8895</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8791</v>
+        <v>1.5562</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0399</v>
+        <v>3.6999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1225</v>
+        <v>1.2249</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1624</v>
+        <v>2.475</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1489</v>
+        <v>-1.2542</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1344</v>
+        <v>-0.3354</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2833</v>
+        <v>-0.9188</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9792</v>
+        <v>2.1543</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3942</v>
+        <v>0.3636</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0851</v>
+        <v>0.2347</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3091</v>
+        <v>0.129</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1578</v>
+        <v>-0.8516</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2754</v>
+        <v>-0.8516</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>B. LOPEZ CAMIÑA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5884</v>
+        <v>3.194</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4317</v>
+        <v>1.5662</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1567</v>
+        <v>1.6278</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4457</v>
+        <v>-0.891</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8895</v>
+        <v>-0.0119</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5562</v>
+        <v>-0.8791</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6999</v>
+        <v>-1.0399</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2249</v>
+        <v>0.1225</v>
       </c>
       <c r="L14" t="n">
-        <v>2.475</v>
+        <v>-1.1624</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2542</v>
+        <v>0.1489</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3354</v>
+        <v>-0.1344</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9188</v>
+        <v>0.2833</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1543</v>
+        <v>0.9792</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.16</v>
+        <v>0.9479</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0723</v>
+        <v>0.3688</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0877</v>
+        <v>0.5792</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8516</v>
+        <v>2.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8516</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>O. CASTAÑO RUBIANES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.277</v>
+        <v>1.7904</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2701</v>
+        <v>4.3854</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0069</v>
+        <v>-2.595</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5473</v>
+        <v>3.5777</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0823</v>
+        <v>0.6522</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.535</v>
+        <v>2.9255</v>
       </c>
       <c r="J15" t="n">
-        <v>2.064</v>
+        <v>5.035</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9428</v>
+        <v>1.1908</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1212</v>
+        <v>3.8443</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5167</v>
+        <v>-1.4573</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1396</v>
+        <v>-0.5385</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6563</v>
+        <v>-0.9188</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5226</v>
+        <v>-0.9772</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1059</v>
+        <v>-0.5576</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4167</v>
+        <v>-0.4196</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1846</v>
+        <v>0.365</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2754</v>
+        <v>3.0415</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4599</v>
+        <v>-2.6765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. CASTAÑO RUBIANES</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1957</v>
+        <v>1.2798</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8737</v>
+        <v>1.2701</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.678</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5777</v>
+        <v>1.5473</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6522</v>
+        <v>2.0823</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9255</v>
+        <v>-0.535</v>
       </c>
       <c r="J16" t="n">
-        <v>5.035</v>
+        <v>2.064</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1908</v>
+        <v>1.9428</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8443</v>
+        <v>0.1212</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4573</v>
+        <v>-0.5167</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5385</v>
+        <v>0.1396</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9188</v>
+        <v>-0.6563</v>
       </c>
       <c r="P16" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.1751</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-3.1336</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5718</v>
+        <v>0.5254</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0692</v>
+        <v>0.1059</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5026</v>
+        <v>0.4195</v>
       </c>
       <c r="V16" t="n">
-        <v>0.365</v>
+        <v>-1.1846</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0415</v>
+        <v>0.2754</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6765</v>
+        <v>-1.4599</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8811</v>
+        <v>0.6968</v>
       </c>
       <c r="E17" t="n">
         <v>0.097</v>
       </c>
       <c r="F17" t="n">
-        <v>0.784</v>
+        <v>0.5997</v>
       </c>
       <c r="G17" t="n">
         <v>1.5501</v>
@@ -1780,13 +1780,13 @@
         <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2185</v>
+        <v>-0.4029</v>
       </c>
       <c r="T17" t="n">
         <v>-0.594</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3755</v>
+        <v>0.1911</v>
       </c>
       <c r="V17" t="n">
         <v>0.3329</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0804</v>
+        <v>-0.5229</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4236</v>
+        <v>-0.6283</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3432</v>
+        <v>0.1054</v>
       </c>
       <c r="G18" t="n">
         <v>1.6812</v>
@@ -1858,13 +1858,13 @@
         <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1969</v>
+        <v>-0.2455</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.09</v>
+        <v>-0.2947</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2869</v>
+        <v>0.0491</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8234</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1356</v>
+        <v>-2.1153</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3122</v>
+        <v>1.5231</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5385</v>
+        <v>0.3602</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3664</v>
+        <v>1.487</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.172</v>
+        <v>-1.1268</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2832</v>
+        <v>0.3249</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6414</v>
+        <v>1.0735</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6418</v>
+        <v>-0.7486</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2552</v>
+        <v>0.0353</v>
       </c>
       <c r="N19" t="n">
-        <v>0.275</v>
+        <v>0.4135</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5302</v>
+        <v>-0.3782</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R19" t="n">
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3384</v>
+        <v>0.0269</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1476</v>
+        <v>-0.2858</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.486</v>
+        <v>0.3127</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1217</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4865</v>
+        <v>-0.8723</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2341</v>
+        <v>-1.2379</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2524</v>
+        <v>0.3656</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9233</v>
+        <v>-1.5385</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2062</v>
+        <v>-0.3664</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7171</v>
+        <v>-1.172</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4025</v>
+        <v>-1.2832</v>
       </c>
       <c r="K20" t="n">
-        <v>0.199</v>
+        <v>-0.6414</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6014</v>
+        <v>-0.6418</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5209</v>
+        <v>-0.2552</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4052</v>
+        <v>0.275</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1157</v>
+        <v>-0.5302</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3085</v>
+        <v>-0.3873</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1476</v>
+        <v>0.0453</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4562</v>
+        <v>-0.4326</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3329</v>
+        <v>-0.1217</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3329</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8358</v>
+        <v>-1.2726</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5247</v>
+        <v>-1.2341</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6889</v>
+        <v>-0.0385</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3602</v>
+        <v>-0.9233</v>
       </c>
       <c r="H21" t="n">
-        <v>1.487</v>
+        <v>-0.2062</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1268</v>
+        <v>-0.7171</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3249</v>
+        <v>-0.4025</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0735</v>
+        <v>0.199</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7486</v>
+        <v>-0.6014</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0353</v>
+        <v>-0.5209</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4135</v>
+        <v>-0.4052</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3782</v>
+        <v>-0.1157</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.5875</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.1543</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2167</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6952</v>
+        <v>0.1476</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5215</v>
+        <v>-0.2423</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6512</v>
+        <v>-2.571</v>
       </c>
       <c r="E22" t="n">
         <v>-2.6754</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0243</v>
+        <v>0.1045</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0137</v>
@@ -2170,13 +2170,13 @@
         <v>0.9792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2612</v>
+        <v>-0.181</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0236</v>
+        <v>0.0566</v>
       </c>
       <c r="V22" t="n">
         <v>-0.397</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0951</v>
+        <v>-5.2675</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3028</v>
+        <v>-4.5075</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7923</v>
+        <v>-0.76</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6295</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2443</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0129</v>
+        <v>-0.2176</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2572</v>
+        <v>0.2895</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5763</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3899</v>
+        <v>-0.02549999999999919</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.341100000000001</v>
+        <v>-1.3411</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.04880000000000029</v>
+        <v>1.315499999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>5.1662</v>
+        <v>5.166200000000001</v>
       </c>
       <c r="H24" t="n">
         <v>7.843</v>
@@ -2302,19 +2302,19 @@
         <v>10.6614</v>
       </c>
       <c r="K24" t="n">
-        <v>7.458000000000001</v>
+        <v>7.458</v>
       </c>
       <c r="L24" t="n">
-        <v>3.203600000000001</v>
+        <v>3.2036</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.495299999999999</v>
+        <v>-5.4953</v>
       </c>
       <c r="N24" t="n">
         <v>0.3853</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.880599999999999</v>
+        <v>-5.880600000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-4.896199999999999</v>
@@ -2326,13 +2326,13 @@
         <v>12.7301</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7171</v>
+        <v>-0.3529</v>
       </c>
       <c r="T24" t="n">
         <v>-1.285</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4321999999999999</v>
+        <v>0.9322</v>
       </c>
       <c r="V24" t="n">
         <v>0.0573999999999999</v>
